--- a/LISTAS_ORDENADAS/MA/Cerrojos Pasadores/PORTACANDADOS.xlsx
+++ b/LISTAS_ORDENADAS/MA/Cerrojos Pasadores/PORTACANDADOS.xlsx
@@ -723,14 +723,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45216.53896266151</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -771,25 +767,6 @@
     <row r="11" ht="17.25" customHeight="1" s="15">
       <c r="E11" s="8" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="15">
       <c r="A31" s="12" t="inlineStr">
         <is>
@@ -821,7 +798,7 @@
       </c>
       <c r="C32" s="17" t="n"/>
       <c r="D32" s="11" t="n">
-        <v>134.59</v>
+        <v>111.234</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="15">
@@ -837,7 +814,7 @@
       </c>
       <c r="C33" s="17" t="n"/>
       <c r="D33" s="10" t="n">
-        <v>192.58</v>
+        <v>159.163</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="15">
@@ -853,7 +830,7 @@
       </c>
       <c r="C34" s="17" t="n"/>
       <c r="D34" s="11" t="n">
-        <v>256.41</v>
+        <v>211.913</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="15">
@@ -869,7 +846,7 @@
       </c>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="10" t="n">
-        <v>263.99</v>
+        <v>218.175</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="15">
@@ -885,7 +862,7 @@
       </c>
       <c r="C36" s="17" t="n"/>
       <c r="D36" s="11" t="n">
-        <v>345.97</v>
+        <v>285.93</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="15">
@@ -901,7 +878,7 @@
       </c>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>395.6</v>
+        <v>326.947</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="15">
@@ -917,7 +894,7 @@
       </c>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="11" t="n">
-        <v>473.73</v>
+        <v>391.516</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="15">
@@ -933,16 +910,9 @@
       </c>
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="11" t="n">
-        <v>564.11</v>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
+        <v>466.211</v>
+      </c>
+    </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
@@ -952,18 +922,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
